--- a/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Regular Gold Savings Fund (FOF).xlsx
+++ b/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Regular Gold Savings Fund (FOF).xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\mumchfnp01\RatingFinance\Factseet Mandates\ICICI PRUDENTIAL FACTSHEET\2025\Feb\Portfolio stage 8\Riskometer updated Portfolio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\mumchfnp01\RatingFinance\Factseet Mandates\ICICI PRUDENTIAL FACTSHEET\2025\June\Portfolio stage 8\Riskometer updated portfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{057F4E2B-22D5-4178-B099-3E62798BB16B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A64EEBB-CAF6-47A9-8A4D-7A374C9816F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
     <t>ICICI Prudential Regular Gold Savings Fund (FOF)</t>
   </si>
   <si>
-    <t>Portfolio as on Jan 31,2025</t>
+    <t>Portfolio as on May 31,2025</t>
   </si>
   <si>
     <t>Company/Issuer/Instrument Name</t>
@@ -85,7 +85,7 @@
     <t>@ As per AMFI Best Practices Guidelines Circular No. 91/ 2020 - 21 dated March 24, 2021 on Valuation of AT-1 Bonds and Tier 2 Bonds, Yield to call is disclosed for AT-1 Bonds and Tier 2 Bonds issued by Banks as provided by Valuation agencies.</t>
   </si>
   <si>
-    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2023/74 dated May 19, 2023.Refer link: https://www.icicipruamc.com/statutory-disclosures/deviation-in-valuation-of-securities</t>
+    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2024/90 dated June 27, 2024. Refer link: https://www.icicipruamc.com/about-us/statutory-disclosures?currentTabFilter=OtherDisclosures&amp;&amp;subCatTabFilter=deviationinvaluationofsecurities</t>
   </si>
   <si>
     <t>As per AMFI Best Practices Guidelines Circular No. AMFI/ 35P/ MEM-COR/ 72 / 2022-23 dated December 31, 2022 on Standard format for disclosure Portfolio YTM for Debt Schemes, Yield of the instrument is disclosed on annualized basis as provided by Valuation agencies.</t>
@@ -326,7 +326,18 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -852,10 +863,10 @@
         <v>12</v>
       </c>
       <c r="F5" s="12">
-        <v>156987.10999999999</v>
+        <v>215059.89</v>
       </c>
       <c r="G5" s="13">
-        <v>0.99631321648240001</v>
+        <v>0.99917623843119996</v>
       </c>
       <c r="H5" s="12" t="s">
         <v>12</v>
@@ -875,13 +886,13 @@
         <v>15</v>
       </c>
       <c r="E6" s="17">
-        <v>220240056</v>
+        <v>261439202</v>
       </c>
       <c r="F6" s="18">
-        <v>156987.10999999999</v>
+        <v>215059.89</v>
       </c>
       <c r="G6" s="19">
-        <v>0.99631321648240001</v>
+        <v>0.99917623843119996</v>
       </c>
       <c r="H6" s="18" t="s">
         <v>12</v>
@@ -912,10 +923,10 @@
         <v>12</v>
       </c>
       <c r="F8" s="12">
-        <v>888.44</v>
+        <v>1396.28</v>
       </c>
       <c r="G8" s="13">
-        <v>5.6384534631000001E-3</v>
+        <v>6.4871687519000003E-3</v>
       </c>
       <c r="H8" s="12" t="s">
         <v>12</v>
@@ -946,10 +957,10 @@
         <v>12</v>
       </c>
       <c r="F10" s="21">
-        <v>-307.52078699998674</v>
+        <v>-1218.9758713100164</v>
       </c>
       <c r="G10" s="22">
-        <v>-1.9516699455844628E-3</v>
+        <v>-5.6634071831525206E-3</v>
       </c>
       <c r="H10" s="21" t="s">
         <v>12</v>
@@ -972,10 +983,10 @@
         <v>12</v>
       </c>
       <c r="F11" s="21">
-        <v>157568.029213</v>
+        <v>215237.19412869</v>
       </c>
       <c r="G11" s="22">
-        <v>0.99999999999991551</v>
+        <v>0.99999999999994749</v>
       </c>
       <c r="H11" s="21" t="s">
         <v>12</v>
